--- a/public/templates/grades-template.xlsx
+++ b/public/templates/grades-template.xlsx
@@ -46,6 +46,7 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00374151"/>
       <sz val="10"/>
     </font>
     <font>
@@ -148,9 +149,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -516,14 +515,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -534,22 +535,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>course_category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>course_code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>semester_year</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>semester</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>grade</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>is_resit</t>
         </is>
       </c>
     </row>
@@ -564,11 +575,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -602,131 +613,187 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>3. index_number and course_code must already exist in the system.</t>
+          <t>3. index_number must match an existing student in the system.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>4. The semester + year combination must match an existing semester.</t>
+          <t>4. course_category + course_code together identify the exact course.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>5. Save as CSV: File → Save As → CSV UTF-8 (Comma delimited) (*.csv)</t>
+          <t xml:space="preserve">   Example: category=OSIS_NEW, code=MATH101 selects the OSIS New version of MATH101.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>6. Go to Bulk Upload → Grade Import and upload the CSV file.</t>
+          <t>5. semester must be FIRST or SECOND.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>7. Grades already entered for a student+course+semester are skipped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+          <t>6. Valid grades: A, B+, B, C+, C, D+, D, F — or P/F for non-scoring courses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>7. is_resit: enter 'true' if this is a resit attempt (doubles credit hours in GPA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Leave blank or enter 'false' for normal first attempts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>8. Save as CSV: File → Save As → CSV UTF-8 (Comma delimited) (*.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>9. Go to Bulk Upload → Grade Import and upload the CSV file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>COLUMN REFERENCE</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>index_number</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Student index number — must exist in the system</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>course_code</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Course code — must exist in the system</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>semester_year</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Academic year e.g. 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>semester</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>FIRST or SECOND</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t>index_number</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Student index number — must exist in the system (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>course_category</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Category of the course: OSIS_OLD, OSIS_NEW, ITS, or OSIS_2 (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>course_code</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Course code e.g. MATH101 — combined with category to find the course (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>semester_year</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Academic year as a 4-digit number e.g. 2023 (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>semester</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>FIRST or SECOND (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>grade</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>A, B+, B, C+, C, D+, D, or F</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>VALID GRADES: A (4.00) | B+ (3.50) | B (3.00) | C+ (2.50) | C (2.00) | D+ (1.50) | D (1.00) | F (0.00)</t>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>A, B+, B, C+, C, D+, D, F for scoring courses — or P, F for non-scoring (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>is_resit</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>true if this is a resit/repeat attempt, false or blank if first attempt (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>NOTE: Duplicate entries (same student + category + code + semester) are automatically skipped.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="15">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A8:B8"/>
